--- a/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26924901971657</v>
+        <v>1.26690264270342</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612561819633923</v>
+        <v>4.629978023907261</v>
       </c>
       <c r="D3" t="n">
-        <v>6.017892627734131</v>
+        <v>6.09254472316506</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89970346708462</v>
+        <v>11.98942538977574</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.42101618117656</v>
+        <v>1.409298322756275</v>
       </c>
       <c r="C4" t="n">
-        <v>5.116260494493704</v>
+        <v>5.152416043732515</v>
       </c>
       <c r="D4" t="n">
-        <v>6.223551086822162</v>
+        <v>6.409148675511707</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76082776249243</v>
+        <v>12.9708630420005</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.623139917738463</v>
+        <v>1.594925741887272</v>
       </c>
       <c r="C5" t="n">
-        <v>5.789682172238223</v>
+        <v>5.814434372841549</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49843281835741</v>
+        <v>6.81516194297995</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9112549083341</v>
+        <v>14.22452205770877</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.85343308735024</v>
+        <v>1.809827816658313</v>
       </c>
       <c r="C6" t="n">
-        <v>6.671721568159314</v>
+        <v>6.63309138601737</v>
       </c>
       <c r="D6" t="n">
-        <v>6.816680196581378</v>
+        <v>7.225865705613507</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34183485209093</v>
+        <v>15.66878490828919</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.102141989436166</v>
+        <v>2.042655867673441</v>
       </c>
       <c r="C7" t="n">
-        <v>7.775190393542822</v>
+        <v>7.639573492993173</v>
       </c>
       <c r="D7" t="n">
-        <v>7.148714371827964</v>
+        <v>7.611539752339534</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02604675480695</v>
+        <v>17.29376911300615</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.301085483491816</v>
+        <v>1.2346420384657</v>
       </c>
       <c r="C8" t="n">
-        <v>5.644995807752862</v>
+        <v>5.363878477192455</v>
       </c>
       <c r="D8" t="n">
-        <v>5.445380070204406</v>
+        <v>5.859157461926046</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39146136144908</v>
+        <v>12.4576779775842</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.62327343368364</v>
+        <v>1.524345606145128</v>
       </c>
       <c r="C9" t="n">
-        <v>7.181488179888706</v>
+        <v>6.721502745383241</v>
       </c>
       <c r="D9" t="n">
-        <v>5.98694897456166</v>
+        <v>6.416829898956575</v>
       </c>
       <c r="E9" t="n">
-        <v>14.79171058813401</v>
+        <v>14.66267825048494</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.953517073338717</v>
+        <v>1.822062890347185</v>
       </c>
       <c r="C10" t="n">
-        <v>8.873665267952855</v>
+        <v>8.296526721743218</v>
       </c>
       <c r="D10" t="n">
-        <v>6.447054855492707</v>
+        <v>6.985444919723593</v>
       </c>
       <c r="E10" t="n">
-        <v>17.27423719678428</v>
+        <v>17.104034531814</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.277577598504841</v>
+        <v>2.120845460619311</v>
       </c>
       <c r="C11" t="n">
-        <v>10.70563549722436</v>
+        <v>10.05575314466496</v>
       </c>
       <c r="D11" t="n">
-        <v>6.923307320014375</v>
+        <v>7.525415659883215</v>
       </c>
       <c r="E11" t="n">
-        <v>19.90652041574357</v>
+        <v>19.70201426516748</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.592030025770624</v>
+        <v>2.406929726215591</v>
       </c>
       <c r="C12" t="n">
-        <v>12.59634469860327</v>
+        <v>11.89204053441407</v>
       </c>
       <c r="D12" t="n">
-        <v>7.338439043992754</v>
+        <v>8.040205230625043</v>
       </c>
       <c r="E12" t="n">
-        <v>22.52681376836664</v>
+        <v>22.3391754912547</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.885499942379572</v>
+        <v>2.669860262456108</v>
       </c>
       <c r="C13" t="n">
-        <v>14.48567456372473</v>
+        <v>13.79737815336362</v>
       </c>
       <c r="D13" t="n">
-        <v>7.771126689196615</v>
+        <v>8.495555393384429</v>
       </c>
       <c r="E13" t="n">
-        <v>25.14230119530092</v>
+        <v>24.96279380920416</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.664396152917788</v>
+        <v>1.543474288185708</v>
       </c>
       <c r="C14" t="n">
-        <v>9.973790911938281</v>
+        <v>9.579835193178122</v>
       </c>
       <c r="D14" t="n">
-        <v>5.925338268981624</v>
+        <v>6.4198347701337</v>
       </c>
       <c r="E14" t="n">
-        <v>17.56352533383769</v>
+        <v>17.54314425149753</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.694202013218721</v>
+        <v>1.5519565883504</v>
       </c>
       <c r="C15" t="n">
-        <v>10.92901179321634</v>
+        <v>10.56808206722705</v>
       </c>
       <c r="D15" t="n">
-        <v>5.891958847037234</v>
+        <v>6.41832287866916</v>
       </c>
       <c r="E15" t="n">
-        <v>18.5151726534723</v>
+        <v>18.53836153424661</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.952666731315778</v>
+        <v>1.766252477233394</v>
       </c>
       <c r="C16" t="n">
-        <v>13.00505475852482</v>
+        <v>12.62903557032125</v>
       </c>
       <c r="D16" t="n">
-        <v>6.271777398856239</v>
+        <v>6.883455305987214</v>
       </c>
       <c r="E16" t="n">
-        <v>21.22949888869683</v>
+        <v>21.27874335354186</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.555392705315264</v>
+        <v>1.391480108614217</v>
       </c>
       <c r="C17" t="n">
-        <v>12.04385503372789</v>
+        <v>11.76067972591495</v>
       </c>
       <c r="D17" t="n">
-        <v>5.753041546886309</v>
+        <v>6.357012734538947</v>
       </c>
       <c r="E17" t="n">
-        <v>19.35228928592947</v>
+        <v>19.50917256906811</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.764318434256028</v>
+        <v>1.552300200046887</v>
       </c>
       <c r="C18" t="n">
-        <v>14.09813265243322</v>
+        <v>13.7831781714338</v>
       </c>
       <c r="D18" t="n">
-        <v>6.119596687220941</v>
+        <v>6.728260628899878</v>
       </c>
       <c r="E18" t="n">
-        <v>21.98204777391019</v>
+        <v>22.06373900038056</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.755836134091336</v>
+        <v>1.528129571568331</v>
       </c>
       <c r="C19" t="n">
-        <v>15.09856301549184</v>
+        <v>14.78604326879896</v>
       </c>
       <c r="D19" t="n">
-        <v>6.171256251418408</v>
+        <v>6.799260622871008</v>
       </c>
       <c r="E19" t="n">
-        <v>23.02565540100159</v>
+        <v>23.11343346323829</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.933188856863522</v>
+        <v>1.669560145842126</v>
       </c>
       <c r="C20" t="n">
-        <v>17.25373484576261</v>
+        <v>16.91400105270801</v>
       </c>
       <c r="D20" t="n">
-        <v>6.507799364434215</v>
+        <v>7.254231961450107</v>
       </c>
       <c r="E20" t="n">
-        <v>25.69472306706035</v>
+        <v>25.83779316000024</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.140211601189288</v>
+        <v>0.9778403483839082</v>
       </c>
       <c r="C21" t="n">
-        <v>12.56660623380819</v>
+        <v>12.31759574610303</v>
       </c>
       <c r="D21" t="n">
-        <v>5.404511294401649</v>
+        <v>6.043589779958153</v>
       </c>
       <c r="E21" t="n">
-        <v>19.11132912939913</v>
+        <v>19.33902587444509</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26690264270342</v>
+        <v>1.284240307160419</v>
       </c>
       <c r="C3" t="n">
-        <v>4.629978023907261</v>
+        <v>4.595715029029049</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09254472316506</v>
+        <v>6.062876307542721</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98942538977574</v>
+        <v>11.94283164373219</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.409298322756275</v>
+        <v>1.468937681687616</v>
       </c>
       <c r="C4" t="n">
-        <v>5.152416043732515</v>
+        <v>5.070501645406088</v>
       </c>
       <c r="D4" t="n">
-        <v>6.409148675511707</v>
+        <v>6.31239838083176</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9708630420005</v>
+        <v>12.85183770792546</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.594925741887272</v>
+        <v>1.712973415882004</v>
       </c>
       <c r="C5" t="n">
-        <v>5.814434372841549</v>
+        <v>5.670716924541967</v>
       </c>
       <c r="D5" t="n">
-        <v>6.81516194297995</v>
+        <v>6.703808991932965</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22452205770877</v>
+        <v>14.08749933235694</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.809827816658313</v>
+        <v>1.983844763565201</v>
       </c>
       <c r="C6" t="n">
-        <v>6.63309138601737</v>
+        <v>6.418382633238499</v>
       </c>
       <c r="D6" t="n">
-        <v>7.225865705613507</v>
+        <v>7.075516495028914</v>
       </c>
       <c r="E6" t="n">
-        <v>15.66878490828919</v>
+        <v>15.47774389183262</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.042655867673441</v>
+        <v>2.274461966017407</v>
       </c>
       <c r="C7" t="n">
-        <v>7.639573492993173</v>
+        <v>7.279694150420091</v>
       </c>
       <c r="D7" t="n">
-        <v>7.611539752339534</v>
+        <v>7.526005229992274</v>
       </c>
       <c r="E7" t="n">
-        <v>17.29376911300615</v>
+        <v>17.08016134642977</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.2346420384657</v>
+        <v>1.445322375929651</v>
       </c>
       <c r="C8" t="n">
-        <v>5.363878477192455</v>
+        <v>4.988454745654813</v>
       </c>
       <c r="D8" t="n">
-        <v>5.859157461926046</v>
+        <v>5.844721616387223</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4576779775842</v>
+        <v>12.27849873797169</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.524345606145128</v>
+        <v>1.820641929056444</v>
       </c>
       <c r="C9" t="n">
-        <v>6.721502745383241</v>
+        <v>6.147246774158953</v>
       </c>
       <c r="D9" t="n">
-        <v>6.416829898956575</v>
+        <v>6.375818583569627</v>
       </c>
       <c r="E9" t="n">
-        <v>14.66267825048494</v>
+        <v>14.34370728678502</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.822062890347185</v>
+        <v>2.212998817023855</v>
       </c>
       <c r="C10" t="n">
-        <v>8.296526721743218</v>
+        <v>7.50276478627179</v>
       </c>
       <c r="D10" t="n">
-        <v>6.985444919723593</v>
+        <v>6.980674663501585</v>
       </c>
       <c r="E10" t="n">
-        <v>17.104034531814</v>
+        <v>16.69643826679723</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.120845460619311</v>
+        <v>2.611797081649272</v>
       </c>
       <c r="C11" t="n">
-        <v>10.05575314466496</v>
+        <v>8.981601362321086</v>
       </c>
       <c r="D11" t="n">
-        <v>7.525415659883215</v>
+        <v>7.540789058021936</v>
       </c>
       <c r="E11" t="n">
-        <v>19.70201426516748</v>
+        <v>19.13418750199229</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.406929726215591</v>
+        <v>3.006723961350706</v>
       </c>
       <c r="C12" t="n">
-        <v>11.89204053441407</v>
+        <v>10.52402116276836</v>
       </c>
       <c r="D12" t="n">
-        <v>8.040205230625043</v>
+        <v>8.127284843174342</v>
       </c>
       <c r="E12" t="n">
-        <v>22.3391754912547</v>
+        <v>21.65802996729341</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.669860262456108</v>
+        <v>3.374665003573852</v>
       </c>
       <c r="C13" t="n">
-        <v>13.79737815336362</v>
+        <v>12.06518828770754</v>
       </c>
       <c r="D13" t="n">
-        <v>8.495555393384429</v>
+        <v>8.605391134987956</v>
       </c>
       <c r="E13" t="n">
-        <v>24.96279380920416</v>
+        <v>24.04524442626935</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.543474288185708</v>
+        <v>1.946236283852962</v>
       </c>
       <c r="C14" t="n">
-        <v>9.579835193178122</v>
+        <v>8.390055150401411</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4198347701337</v>
+        <v>6.532028897775025</v>
       </c>
       <c r="E14" t="n">
-        <v>17.54314425149753</v>
+        <v>16.8683203320294</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.5519565883504</v>
+        <v>1.992103536595373</v>
       </c>
       <c r="C15" t="n">
-        <v>10.56808206722705</v>
+        <v>9.067402161469456</v>
       </c>
       <c r="D15" t="n">
-        <v>6.41832287866916</v>
+        <v>6.583217223074454</v>
       </c>
       <c r="E15" t="n">
-        <v>18.53836153424661</v>
+        <v>17.64272292113928</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.766252477233394</v>
+        <v>2.316492613032604</v>
       </c>
       <c r="C16" t="n">
-        <v>12.62903557032125</v>
+        <v>10.74514026568796</v>
       </c>
       <c r="D16" t="n">
-        <v>6.883455305987214</v>
+        <v>7.087462478929702</v>
       </c>
       <c r="E16" t="n">
-        <v>21.27874335354186</v>
+        <v>20.14909535765026</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.391480108614217</v>
+        <v>1.859538144090926</v>
       </c>
       <c r="C17" t="n">
-        <v>11.76067972591495</v>
+        <v>9.95958502265783</v>
       </c>
       <c r="D17" t="n">
-        <v>6.357012734538947</v>
+        <v>6.59719731038293</v>
       </c>
       <c r="E17" t="n">
-        <v>19.50917256906811</v>
+        <v>18.41632047713168</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.552300200046887</v>
+        <v>2.130107811381347</v>
       </c>
       <c r="C18" t="n">
-        <v>13.7831781714338</v>
+        <v>11.66943609428224</v>
       </c>
       <c r="D18" t="n">
-        <v>6.728260628899878</v>
+        <v>7.062810794076064</v>
       </c>
       <c r="E18" t="n">
-        <v>22.06373900038056</v>
+        <v>20.86235469973965</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.528129571568331</v>
+        <v>2.145943401850849</v>
       </c>
       <c r="C19" t="n">
-        <v>14.78604326879896</v>
+        <v>12.53575972094076</v>
       </c>
       <c r="D19" t="n">
-        <v>6.799260622871008</v>
+        <v>7.172422925255219</v>
       </c>
       <c r="E19" t="n">
-        <v>23.11343346323829</v>
+        <v>21.85412604804682</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.669560145842126</v>
+        <v>2.397526068541136</v>
       </c>
       <c r="C20" t="n">
-        <v>16.91400105270801</v>
+        <v>14.47021503234276</v>
       </c>
       <c r="D20" t="n">
-        <v>7.254231961450107</v>
+        <v>7.64358328347735</v>
       </c>
       <c r="E20" t="n">
-        <v>25.83779316000024</v>
+        <v>24.51132438436124</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9778403483839082</v>
+        <v>1.433282925861046</v>
       </c>
       <c r="C21" t="n">
-        <v>12.31759574610303</v>
+        <v>10.69475697350601</v>
       </c>
       <c r="D21" t="n">
-        <v>6.043589779958153</v>
+        <v>6.389714750567408</v>
       </c>
       <c r="E21" t="n">
-        <v>19.33902587444509</v>
+        <v>18.51775464993447</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_80_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.284240307160419</v>
+        <v>2.624417302353145</v>
       </c>
       <c r="C3" t="n">
-        <v>4.595715029029049</v>
+        <v>7.652298372447566</v>
       </c>
       <c r="D3" t="n">
-        <v>6.062876307542721</v>
+        <v>8.148582290122288</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94283164373219</v>
+        <v>18.425297964923</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.468937681687616</v>
+        <v>1.146610844443075</v>
       </c>
       <c r="C4" t="n">
-        <v>5.070501645406088</v>
+        <v>4.439916856562117</v>
       </c>
       <c r="D4" t="n">
-        <v>6.31239838083176</v>
+        <v>5.741830525817086</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85183770792546</v>
+        <v>11.32835822682228</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.712973415882004</v>
+        <v>1.302275532741411</v>
       </c>
       <c r="C5" t="n">
-        <v>5.670716924541967</v>
+        <v>5.105405154641001</v>
       </c>
       <c r="D5" t="n">
-        <v>6.703808991932965</v>
+        <v>6.067145599348294</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08749933235694</v>
+        <v>12.47482628673071</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.983844763565201</v>
+        <v>1.474623512713107</v>
       </c>
       <c r="C6" t="n">
-        <v>6.418382633238499</v>
+        <v>6.038886807821281</v>
       </c>
       <c r="D6" t="n">
-        <v>7.075516495028914</v>
+        <v>6.430843299561691</v>
       </c>
       <c r="E6" t="n">
-        <v>15.47774389183262</v>
+        <v>13.94435362009608</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.274461966017407</v>
+        <v>1.643343706348625</v>
       </c>
       <c r="C7" t="n">
-        <v>7.279694150420091</v>
+        <v>7.202205137186514</v>
       </c>
       <c r="D7" t="n">
-        <v>7.526005229992274</v>
+        <v>6.77382274495079</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08016134642977</v>
+        <v>15.61937158848593</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.445322375929651</v>
+        <v>1.821191893363594</v>
       </c>
       <c r="C8" t="n">
-        <v>4.988454745654813</v>
+        <v>8.562427934695053</v>
       </c>
       <c r="D8" t="n">
-        <v>5.844721616387223</v>
+        <v>7.194252289109285</v>
       </c>
       <c r="E8" t="n">
-        <v>12.27849873797169</v>
+        <v>17.57787211716793</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.820641929056444</v>
+        <v>1.986005374610531</v>
       </c>
       <c r="C9" t="n">
-        <v>6.147246774158953</v>
+        <v>10.04918416317209</v>
       </c>
       <c r="D9" t="n">
-        <v>6.375818583569627</v>
+        <v>7.585516381139526</v>
       </c>
       <c r="E9" t="n">
-        <v>14.34370728678502</v>
+        <v>19.62070591892214</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.212998817023855</v>
+        <v>1.211123237867035</v>
       </c>
       <c r="C10" t="n">
-        <v>7.50276478627179</v>
+        <v>7.302975734965962</v>
       </c>
       <c r="D10" t="n">
-        <v>6.980674663501585</v>
+        <v>5.972285444198707</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69643826679723</v>
+        <v>14.4863844170317</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.611797081649272</v>
+        <v>1.157274376289098</v>
       </c>
       <c r="C11" t="n">
-        <v>8.981601362321086</v>
+        <v>7.94641318032932</v>
       </c>
       <c r="D11" t="n">
-        <v>7.540789058021936</v>
+        <v>5.837766373762808</v>
       </c>
       <c r="E11" t="n">
-        <v>19.13418750199229</v>
+        <v>14.94145393038123</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.006723961350706</v>
+        <v>1.261467260140812</v>
       </c>
       <c r="C12" t="n">
-        <v>10.52402116276836</v>
+        <v>9.537845843867485</v>
       </c>
       <c r="D12" t="n">
-        <v>8.127284843174342</v>
+        <v>6.215052016504858</v>
       </c>
       <c r="E12" t="n">
-        <v>21.65802996729341</v>
+        <v>17.01436512051315</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.374665003573852</v>
+        <v>0.9959634110043042</v>
       </c>
       <c r="C13" t="n">
-        <v>12.06518828770754</v>
+        <v>9.198602924665</v>
       </c>
       <c r="D13" t="n">
-        <v>8.605391134987956</v>
+        <v>5.662622583325177</v>
       </c>
       <c r="E13" t="n">
-        <v>24.04524442626935</v>
+        <v>15.85718891899448</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.946236283852962</v>
+        <v>1.084821395715683</v>
       </c>
       <c r="C14" t="n">
-        <v>8.390055150401411</v>
+        <v>10.89358051857008</v>
       </c>
       <c r="D14" t="n">
-        <v>6.532028897775025</v>
+        <v>6.00022598386157</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8683203320294</v>
+        <v>17.97862789814733</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.992103536595373</v>
+        <v>1.055221702432642</v>
       </c>
       <c r="C15" t="n">
-        <v>9.067402161469456</v>
+        <v>11.8934316504832</v>
       </c>
       <c r="D15" t="n">
-        <v>6.583217223074454</v>
+        <v>6.028029078845841</v>
       </c>
       <c r="E15" t="n">
-        <v>17.64272292113928</v>
+        <v>18.97668243176168</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.316492613032604</v>
+        <v>1.161289724399467</v>
       </c>
       <c r="C16" t="n">
-        <v>10.74514026568796</v>
+        <v>13.9543164312381</v>
       </c>
       <c r="D16" t="n">
-        <v>7.087462478929702</v>
+        <v>6.416457558031091</v>
       </c>
       <c r="E16" t="n">
-        <v>20.14909535765026</v>
+        <v>21.53206371366866</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.859538144090926</v>
+        <v>0.6946454056168732</v>
       </c>
       <c r="C17" t="n">
-        <v>9.95958502265783</v>
+        <v>10.47741766673985</v>
       </c>
       <c r="D17" t="n">
-        <v>6.59719731038293</v>
+        <v>5.316163818496478</v>
       </c>
       <c r="E17" t="n">
-        <v>18.41632047713168</v>
+        <v>16.4882268908532</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.130107811381347</v>
+        <v>0.5615204169210056</v>
       </c>
       <c r="C18" t="n">
-        <v>11.66943609428224</v>
+        <v>9.554859531582084</v>
       </c>
       <c r="D18" t="n">
-        <v>7.062810794076064</v>
+        <v>4.813852605618599</v>
       </c>
       <c r="E18" t="n">
-        <v>20.86235469973965</v>
+        <v>14.93023255412169</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.145943401850849</v>
+        <v>0.6620808342670065</v>
       </c>
       <c r="C19" t="n">
-        <v>12.53575972094076</v>
+        <v>11.87125396984426</v>
       </c>
       <c r="D19" t="n">
-        <v>7.172422925255219</v>
+        <v>5.306572143425988</v>
       </c>
       <c r="E19" t="n">
-        <v>21.85412604804682</v>
+        <v>17.83990694753726</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.397526068541136</v>
+        <v>0.755209421491859</v>
       </c>
       <c r="C20" t="n">
-        <v>14.47021503234276</v>
+        <v>14.26948689673246</v>
       </c>
       <c r="D20" t="n">
-        <v>7.64358328347735</v>
+        <v>5.75813681747135</v>
       </c>
       <c r="E20" t="n">
-        <v>24.51132438436124</v>
+        <v>20.78283313569566</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.433282925861046</v>
+        <v>0.8314912181118361</v>
       </c>
       <c r="C21" t="n">
-        <v>10.69475697350601</v>
+        <v>16.68066907583966</v>
       </c>
       <c r="D21" t="n">
-        <v>6.389714750567408</v>
+        <v>6.206127929873253</v>
       </c>
       <c r="E21" t="n">
-        <v>18.51775464993447</v>
+        <v>23.71828822382475</v>
       </c>
     </row>
   </sheetData>
